--- a/templete/templete.eWES.xlsx
+++ b/templete/templete.eWES.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mioka\AppData\Local\Temp\scp35178\data1\labTools\worksheet\version\v3.0.0\templete\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mioka\AppData\Local\Temp\scp36733\data1\labTools\worksheet\version\v3.1.0\templete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C72075-376D-4061-8B7F-36AF05F6A0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF6E52B-5912-4999-8ECF-B093A6115EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21555" yWindow="2550" windowWidth="21075" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="work_sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">work_sheet!$A$1:$T$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">work_sheet!$A$1:$T$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="57">
   <si>
     <t>run_id</t>
   </si>
@@ -232,16 +232,6 @@
   </si>
   <si>
     <t>)            WET(</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>レポートに文字化けがないか確認する</t>
-    <rPh sb="5" eb="8">
-      <t>モジバ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カクニン</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -490,13 +480,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>パイプラインで生成されたレポートをプリントアウトする（2in1,白黒両面印刷）</t>
-    <rPh sb="7" eb="9">
-      <t>セイセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>OncoStationで SendMail ⇒ Upload Report ボタンを押下する</t>
     <rPh sb="42" eb="44">
       <t>オウカ</t>
@@ -541,6 +524,10 @@
     <rPh sb="39" eb="41">
       <t>ツイカ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レポートをプリントアウトする（2in1,白黒両面印刷）</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1348,7 +1335,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:T56"/>
+  <dimension ref="B1:T55"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -1368,7 +1355,7 @@
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:20" x14ac:dyDescent="0.4">
@@ -1399,7 +1386,7 @@
       </c>
       <c r="Q2" s="27"/>
       <c r="R2" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S2" s="19"/>
       <c r="T2" s="19"/>
@@ -1569,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D11" s="44"/>
       <c r="E11" s="44"/>
@@ -1596,7 +1583,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D12" s="44"/>
       <c r="E12" s="44"/>
@@ -1623,7 +1610,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D13" s="44"/>
       <c r="E13" s="44"/>
@@ -1677,7 +1664,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" s="44"/>
       <c r="E15" s="44"/>
@@ -1702,36 +1689,36 @@
     <row r="16" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="50"/>
       <c r="C16" s="70" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
       <c r="F16" s="75" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G16" s="76"/>
       <c r="H16" s="76"/>
       <c r="I16" s="77"/>
       <c r="J16" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="K16" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="L16" s="70" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M16" s="70"/>
       <c r="N16" s="70" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O16" s="70"/>
       <c r="P16" s="70"/>
       <c r="Q16" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="R16" s="13" t="s">
         <v>46</v>
-      </c>
-      <c r="R16" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="S16" s="55"/>
       <c r="T16" s="56"/>
@@ -1739,12 +1726,12 @@
     <row r="17" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="50"/>
       <c r="C17" s="59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="59"/>
       <c r="F17" s="23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G17" s="74"/>
       <c r="H17" s="74"/>
@@ -1756,11 +1743,11 @@
         <v>9</v>
       </c>
       <c r="L17" s="59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M17" s="59"/>
       <c r="N17" s="59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O17" s="59"/>
       <c r="P17" s="59"/>
@@ -1776,12 +1763,12 @@
     <row r="18" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="50"/>
       <c r="C18" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="59"/>
       <c r="F18" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G18" s="74"/>
       <c r="H18" s="74"/>
@@ -1793,11 +1780,11 @@
         <v>9</v>
       </c>
       <c r="L18" s="59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M18" s="59"/>
       <c r="N18" s="59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O18" s="59"/>
       <c r="P18" s="59"/>
@@ -1813,12 +1800,12 @@
     <row r="19" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="51"/>
       <c r="C19" s="59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" s="59"/>
       <c r="E19" s="59"/>
       <c r="F19" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G19" s="74"/>
       <c r="H19" s="74"/>
@@ -1830,11 +1817,11 @@
         <v>9</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M19" s="24"/>
       <c r="N19" s="59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O19" s="59"/>
       <c r="P19" s="59"/>
@@ -1847,203 +1834,199 @@
       <c r="S19" s="57"/>
       <c r="T19" s="58"/>
     </row>
-    <row r="20" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B20" s="2">
         <v>6</v>
       </c>
-      <c r="C20" s="78" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="79"/>
-      <c r="O20" s="79"/>
-      <c r="P20" s="79"/>
-      <c r="Q20" s="79"/>
-      <c r="R20" s="80"/>
+      <c r="C20" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="60"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="60"/>
+      <c r="R20" s="60"/>
       <c r="S20" s="23" t="s">
         <v>9</v>
       </c>
       <c r="T20" s="24"/>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B21" s="2">
+      <c r="B21" s="49">
         <v>7</v>
       </c>
-      <c r="C21" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="44"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="3" t="s">
+      <c r="C21" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="T21" s="3" t="s">
+      <c r="T21" s="36"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.4">
+      <c r="B22" s="50"/>
+      <c r="C22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="56"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.4">
+      <c r="B23" s="51"/>
+      <c r="C23" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="58"/>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.4">
+      <c r="B24" s="2">
+        <v>8</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="44"/>
+      <c r="O24" s="44"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="45"/>
+      <c r="S24" s="23" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B22" s="2">
-        <v>8</v>
-      </c>
-      <c r="C22" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="44"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="44"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="3" t="s">
+      <c r="T24" s="24"/>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.4">
+      <c r="B25" s="2">
         <v>9</v>
       </c>
-      <c r="T22" s="3" t="s">
+      <c r="C25" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="22"/>
+      <c r="S25" s="23" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B23" s="2">
+      <c r="T25" s="24"/>
+    </row>
+    <row r="26" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="2">
+        <v>10</v>
+      </c>
+      <c r="C26" s="78" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="79"/>
+      <c r="G26" s="79"/>
+      <c r="H26" s="79"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="79"/>
+      <c r="K26" s="79"/>
+      <c r="L26" s="79"/>
+      <c r="M26" s="79"/>
+      <c r="N26" s="79"/>
+      <c r="O26" s="79"/>
+      <c r="P26" s="79"/>
+      <c r="Q26" s="79"/>
+      <c r="R26" s="80"/>
+      <c r="S26" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="60"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="60"/>
-      <c r="O23" s="60"/>
-      <c r="P23" s="60"/>
-      <c r="Q23" s="60"/>
-      <c r="R23" s="60"/>
-      <c r="S23" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="T23" s="24"/>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B24" s="49">
-        <v>10</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="T24" s="36"/>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B25" s="50"/>
-      <c r="C25" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="18"/>
-      <c r="S25" s="55"/>
-      <c r="T25" s="56"/>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B26" s="51"/>
-      <c r="C26" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
-      <c r="P26" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="57"/>
-      <c r="T26" s="58"/>
+      <c r="T26" s="24"/>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B27" s="2">
         <v>11</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D27" s="21"/>
       <c r="E27" s="21"/>
@@ -2070,7 +2053,7 @@
         <v>12</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D28" s="21"/>
       <c r="E28" s="21"/>
@@ -2093,75 +2076,69 @@
       <c r="T28" s="24"/>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B29" s="2">
-        <v>13</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="22"/>
-      <c r="S29" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="T29" s="24"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B30" s="4"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="8"/>
-      <c r="S30" s="8"/>
-      <c r="T30" s="8"/>
+      <c r="B30" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="62"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="62"/>
+      <c r="P30" s="62"/>
+      <c r="Q30" s="62"/>
+      <c r="R30" s="62"/>
+      <c r="S30" s="62"/>
+      <c r="T30" s="63"/>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B31" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="62"/>
-      <c r="K31" s="62"/>
-      <c r="L31" s="62"/>
-      <c r="M31" s="62"/>
-      <c r="N31" s="62"/>
-      <c r="O31" s="62"/>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="62"/>
-      <c r="R31" s="62"/>
-      <c r="S31" s="62"/>
-      <c r="T31" s="63"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="65"/>
+      <c r="J31" s="65"/>
+      <c r="K31" s="65"/>
+      <c r="L31" s="65"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="65"/>
+      <c r="O31" s="65"/>
+      <c r="P31" s="65"/>
+      <c r="Q31" s="65"/>
+      <c r="R31" s="65"/>
+      <c r="S31" s="65"/>
+      <c r="T31" s="66"/>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B32" s="64"/>
@@ -2206,69 +2183,69 @@
       <c r="T33" s="66"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B34" s="64"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="65"/>
-      <c r="H34" s="65"/>
-      <c r="I34" s="65"/>
-      <c r="J34" s="65"/>
-      <c r="K34" s="65"/>
-      <c r="L34" s="65"/>
-      <c r="M34" s="65"/>
-      <c r="N34" s="65"/>
-      <c r="O34" s="65"/>
-      <c r="P34" s="65"/>
-      <c r="Q34" s="65"/>
-      <c r="R34" s="65"/>
-      <c r="S34" s="65"/>
-      <c r="T34" s="66"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="68"/>
+      <c r="H34" s="68"/>
+      <c r="I34" s="68"/>
+      <c r="J34" s="68"/>
+      <c r="K34" s="68"/>
+      <c r="L34" s="68"/>
+      <c r="M34" s="68"/>
+      <c r="N34" s="68"/>
+      <c r="O34" s="68"/>
+      <c r="P34" s="68"/>
+      <c r="Q34" s="68"/>
+      <c r="R34" s="68"/>
+      <c r="S34" s="68"/>
+      <c r="T34" s="69"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B35" s="67"/>
-      <c r="C35" s="68"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
-      <c r="H35" s="68"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="68"/>
-      <c r="L35" s="68"/>
-      <c r="M35" s="68"/>
-      <c r="N35" s="68"/>
-      <c r="O35" s="68"/>
-      <c r="P35" s="68"/>
-      <c r="Q35" s="68"/>
-      <c r="R35" s="68"/>
-      <c r="S35" s="68"/>
-      <c r="T35" s="69"/>
+      <c r="B35" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="62"/>
+      <c r="K35" s="62"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="62"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="62"/>
+      <c r="R35" s="62"/>
+      <c r="S35" s="62"/>
+      <c r="T35" s="63"/>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B36" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="62"/>
-      <c r="D36" s="62"/>
-      <c r="E36" s="62"/>
-      <c r="F36" s="62"/>
-      <c r="G36" s="62"/>
-      <c r="H36" s="62"/>
-      <c r="I36" s="62"/>
-      <c r="J36" s="62"/>
-      <c r="K36" s="62"/>
-      <c r="L36" s="62"/>
-      <c r="M36" s="62"/>
-      <c r="N36" s="62"/>
-      <c r="O36" s="62"/>
-      <c r="P36" s="62"/>
-      <c r="Q36" s="62"/>
-      <c r="R36" s="62"/>
-      <c r="S36" s="62"/>
-      <c r="T36" s="63"/>
+      <c r="B36" s="64"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="65"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="65"/>
+      <c r="O36" s="65"/>
+      <c r="P36" s="65"/>
+      <c r="Q36" s="65"/>
+      <c r="R36" s="65"/>
+      <c r="S36" s="65"/>
+      <c r="T36" s="66"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B37" s="64"/>
@@ -2313,69 +2290,69 @@
       <c r="T38" s="66"/>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B39" s="64"/>
-      <c r="C39" s="65"/>
-      <c r="D39" s="65"/>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
-      <c r="I39" s="65"/>
-      <c r="J39" s="65"/>
-      <c r="K39" s="65"/>
-      <c r="L39" s="65"/>
-      <c r="M39" s="65"/>
-      <c r="N39" s="65"/>
-      <c r="O39" s="65"/>
-      <c r="P39" s="65"/>
-      <c r="Q39" s="65"/>
-      <c r="R39" s="65"/>
-      <c r="S39" s="65"/>
-      <c r="T39" s="66"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="68"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="68"/>
+      <c r="J39" s="68"/>
+      <c r="K39" s="68"/>
+      <c r="L39" s="68"/>
+      <c r="M39" s="68"/>
+      <c r="N39" s="68"/>
+      <c r="O39" s="68"/>
+      <c r="P39" s="68"/>
+      <c r="Q39" s="68"/>
+      <c r="R39" s="68"/>
+      <c r="S39" s="68"/>
+      <c r="T39" s="69"/>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B40" s="67"/>
-      <c r="C40" s="68"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="68"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="68"/>
-      <c r="O40" s="68"/>
-      <c r="P40" s="68"/>
-      <c r="Q40" s="68"/>
-      <c r="R40" s="68"/>
-      <c r="S40" s="68"/>
-      <c r="T40" s="69"/>
+      <c r="B40" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="62"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="62"/>
+      <c r="M40" s="62"/>
+      <c r="N40" s="62"/>
+      <c r="O40" s="62"/>
+      <c r="P40" s="62"/>
+      <c r="Q40" s="62"/>
+      <c r="R40" s="62"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="63"/>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B41" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="62"/>
-      <c r="D41" s="62"/>
-      <c r="E41" s="62"/>
-      <c r="F41" s="62"/>
-      <c r="G41" s="62"/>
-      <c r="H41" s="62"/>
-      <c r="I41" s="62"/>
-      <c r="J41" s="62"/>
-      <c r="K41" s="62"/>
-      <c r="L41" s="62"/>
-      <c r="M41" s="62"/>
-      <c r="N41" s="62"/>
-      <c r="O41" s="62"/>
-      <c r="P41" s="62"/>
-      <c r="Q41" s="62"/>
-      <c r="R41" s="62"/>
-      <c r="S41" s="62"/>
-      <c r="T41" s="63"/>
+      <c r="B41" s="64"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="65"/>
+      <c r="L41" s="65"/>
+      <c r="M41" s="65"/>
+      <c r="N41" s="65"/>
+      <c r="O41" s="65"/>
+      <c r="P41" s="65"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="65"/>
+      <c r="S41" s="65"/>
+      <c r="T41" s="66"/>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B42" s="64"/>
@@ -2546,56 +2523,60 @@
       <c r="T49" s="66"/>
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B50" s="64"/>
-      <c r="C50" s="65"/>
-      <c r="D50" s="65"/>
-      <c r="E50" s="65"/>
-      <c r="F50" s="65"/>
-      <c r="G50" s="65"/>
-      <c r="H50" s="65"/>
-      <c r="I50" s="65"/>
-      <c r="J50" s="65"/>
-      <c r="K50" s="65"/>
-      <c r="L50" s="65"/>
-      <c r="M50" s="65"/>
-      <c r="N50" s="65"/>
-      <c r="O50" s="65"/>
-      <c r="P50" s="65"/>
-      <c r="Q50" s="65"/>
-      <c r="R50" s="65"/>
-      <c r="S50" s="65"/>
-      <c r="T50" s="66"/>
-    </row>
-    <row r="51" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B51" s="67"/>
-      <c r="C51" s="68"/>
-      <c r="D51" s="68"/>
-      <c r="E51" s="68"/>
-      <c r="F51" s="68"/>
-      <c r="G51" s="68"/>
-      <c r="H51" s="68"/>
-      <c r="I51" s="68"/>
-      <c r="J51" s="68"/>
-      <c r="K51" s="68"/>
-      <c r="L51" s="68"/>
-      <c r="M51" s="68"/>
-      <c r="N51" s="68"/>
-      <c r="O51" s="68"/>
-      <c r="P51" s="68"/>
-      <c r="Q51" s="68"/>
-      <c r="R51" s="68"/>
-      <c r="S51" s="68"/>
-      <c r="T51" s="69"/>
-    </row>
-    <row r="53" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B53" s="14" t="s">
+      <c r="B50" s="67"/>
+      <c r="C50" s="68"/>
+      <c r="D50" s="68"/>
+      <c r="E50" s="68"/>
+      <c r="F50" s="68"/>
+      <c r="G50" s="68"/>
+      <c r="H50" s="68"/>
+      <c r="I50" s="68"/>
+      <c r="J50" s="68"/>
+      <c r="K50" s="68"/>
+      <c r="L50" s="68"/>
+      <c r="M50" s="68"/>
+      <c r="N50" s="68"/>
+      <c r="O50" s="68"/>
+      <c r="P50" s="68"/>
+      <c r="Q50" s="68"/>
+      <c r="R50" s="68"/>
+      <c r="S50" s="68"/>
+      <c r="T50" s="69"/>
+    </row>
+    <row r="52" spans="2:20" x14ac:dyDescent="0.4">
+      <c r="B52" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C53" s="29"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="28" t="s">
-        <v>31</v>
-      </c>
+      <c r="C52" s="29"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="4"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="S52" s="29"/>
+      <c r="T52" s="15"/>
+    </row>
+    <row r="53" spans="2:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B53" s="54"/>
+      <c r="C53" s="71"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="28"/>
       <c r="F53" s="28"/>
       <c r="G53" s="28"/>
       <c r="H53" s="4"/>
@@ -2604,22 +2585,18 @@
       <c r="K53"/>
       <c r="L53"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
-      <c r="Q53" s="28"/>
-      <c r="R53" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="S53" s="29"/>
-      <c r="T53" s="15"/>
+      <c r="N53" s="28"/>
+      <c r="O53" s="36"/>
+      <c r="P53" s="36"/>
+      <c r="Q53" s="37"/>
+      <c r="R53" s="28"/>
+      <c r="S53" s="36"/>
+      <c r="T53" s="37"/>
     </row>
     <row r="54" spans="2:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="54"/>
-      <c r="C54" s="71"/>
-      <c r="D54" s="36"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="72"/>
+      <c r="D54" s="56"/>
       <c r="E54" s="28"/>
       <c r="F54" s="28"/>
       <c r="G54" s="28"/>
@@ -2629,18 +2606,18 @@
       <c r="K54"/>
       <c r="L54"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="28"/>
-      <c r="O54" s="36"/>
-      <c r="P54" s="36"/>
-      <c r="Q54" s="37"/>
-      <c r="R54" s="28"/>
-      <c r="S54" s="36"/>
-      <c r="T54" s="37"/>
-    </row>
-    <row r="55" spans="2:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="55"/>
-      <c r="C55" s="72"/>
-      <c r="D55" s="56"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="39"/>
+      <c r="P54" s="39"/>
+      <c r="Q54" s="40"/>
+      <c r="R54" s="38"/>
+      <c r="S54" s="39"/>
+      <c r="T54" s="40"/>
+    </row>
+    <row r="55" spans="2:20" x14ac:dyDescent="0.4">
+      <c r="B55" s="57"/>
+      <c r="C55" s="73"/>
+      <c r="D55" s="58"/>
       <c r="E55" s="28"/>
       <c r="F55" s="28"/>
       <c r="G55" s="28"/>
@@ -2649,30 +2626,10 @@
       <c r="J55"/>
       <c r="K55"/>
       <c r="L55"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="38"/>
-      <c r="O55" s="39"/>
-      <c r="P55" s="39"/>
-      <c r="Q55" s="40"/>
-      <c r="R55" s="38"/>
-      <c r="S55" s="39"/>
-      <c r="T55" s="40"/>
-    </row>
-    <row r="56" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B56" s="57"/>
-      <c r="C56" s="73"/>
-      <c r="D56" s="58"/>
-      <c r="E56" s="28"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="4"/>
-      <c r="I56"/>
-      <c r="J56"/>
-      <c r="K56"/>
-      <c r="L56"/>
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="S24:T24"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="N3:O3"/>
@@ -2686,7 +2643,7 @@
     <mergeCell ref="L18:M18"/>
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="L16:M16"/>
-    <mergeCell ref="E54:G56"/>
+    <mergeCell ref="E53:G55"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="B15:B19"/>
     <mergeCell ref="C18:E18"/>
@@ -2698,28 +2655,28 @@
     <mergeCell ref="F18:I18"/>
     <mergeCell ref="F17:I17"/>
     <mergeCell ref="F16:I16"/>
+    <mergeCell ref="C26:R26"/>
+    <mergeCell ref="B53:D55"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="N53:Q54"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="S21:T23"/>
     <mergeCell ref="C20:R20"/>
-    <mergeCell ref="B54:D56"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="N54:Q55"/>
-    <mergeCell ref="S24:T26"/>
-    <mergeCell ref="C23:R23"/>
-    <mergeCell ref="R54:T55"/>
-    <mergeCell ref="C22:R22"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="N53:Q53"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="C29:R29"/>
-    <mergeCell ref="C27:R27"/>
-    <mergeCell ref="B41:T51"/>
-    <mergeCell ref="B36:T40"/>
-    <mergeCell ref="B31:T35"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="C21:R21"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="R53:T54"/>
+    <mergeCell ref="C24:R24"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="N52:Q52"/>
+    <mergeCell ref="R52:T52"/>
+    <mergeCell ref="C28:R28"/>
+    <mergeCell ref="C25:R25"/>
+    <mergeCell ref="B40:T50"/>
+    <mergeCell ref="B35:T39"/>
+    <mergeCell ref="B30:T34"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="E52:G52"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="C23:I23"/>
     <mergeCell ref="S14:T14"/>
     <mergeCell ref="C15:R15"/>
     <mergeCell ref="C14:R14"/>
@@ -2727,8 +2684,7 @@
     <mergeCell ref="N19:P19"/>
     <mergeCell ref="N18:P18"/>
     <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="N23:O23"/>
     <mergeCell ref="S10:T10"/>
     <mergeCell ref="C13:R13"/>
     <mergeCell ref="S11:T11"/>
@@ -2738,17 +2694,17 @@
     <mergeCell ref="S12:T12"/>
     <mergeCell ref="C11:R11"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="C25:R25"/>
+    <mergeCell ref="C22:R22"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="C28:R28"/>
-    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="C27:R27"/>
+    <mergeCell ref="S27:T27"/>
     <mergeCell ref="D2:K2"/>
     <mergeCell ref="E6:G8"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="D3:K3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="C24:R24"/>
+    <mergeCell ref="C21:R21"/>
     <mergeCell ref="R6:T7"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D8"/>
@@ -2757,7 +2713,7 @@
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.55118110236220474" bottom="0.55118110236220474" header="0.11811023622047245" footer="0.11811023622047245"/>
-  <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="71" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;LGxC-A-PR10-F01&amp;R版: 01</oddFooter>
   </headerFooter>
